--- a/salida/inventario.xlsx
+++ b/salida/inventario.xlsx
@@ -435,7 +435,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10</v>
+        <v>22222</v>
       </c>
     </row>
     <row r="5">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16000</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/salida/inventario.xlsx
+++ b/salida/inventario.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,11 +431,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>cam</t>
+          <t>camara</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -445,27 +445,17 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>cable</t>
+          <t>rollo de cable</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22222</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>switch</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
